--- a/www/variables_names.xlsx
+++ b/www/variables_names.xlsx
@@ -351,13 +351,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A51"/>
+  <dimension ref="A1:A86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable_Names</t>
+          <t>variable_name</t>
         </is>
       </c>
     </row>
@@ -385,327 +385,572 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>priority_area</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>location</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>level</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>training_date</t>
+          <t>type</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reporter_name</t>
+          <t>training_date</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>reporter_email</t>
+          <t>reporter_name</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>reporter_function</t>
+          <t>reporter_email</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>participants_invited</t>
+          <t>reporter_function</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>participants_invited_aps</t>
+          <t>participants_invited</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>participants_invited_experts</t>
+          <t>participants_invited_program_mentors</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>participants_invited_doctors</t>
+          <t>participants_invited_districts_mentors</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>participants_invited_nurses</t>
+          <t>participants_invited_doctors</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>participants_invited_acrr</t>
+          <t>participants_invited_nurses</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>participants_invited_lab</t>
+          <t>participants_invited_meo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>participants_attended</t>
+          <t>participants_invited_mem</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>participants_attended_aps</t>
+          <t>participants_invited_lab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>participants_attended_experts</t>
+          <t>participants_invited_stockmgmt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>participants_attended_doctors</t>
+          <t>participants_invited_dataclerk</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>participants_attended_nurses</t>
+          <t>participants_invited_aps</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>participants_attended_acrr</t>
+          <t>participants_invited_facilities_staff</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>participants_attended_lab</t>
+          <t>participants_invited_districts_staff</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>participants_invited_moh</t>
+          <t>participants_invited_other_org_staff</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>participants_invited_asdf</t>
+          <t>participants_invited_cbo</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>participants_invited_egpaf</t>
+          <t>participants_invited_chw</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>participants_invited_non_pepfar</t>
+          <t>participants_invited_mothers_mentors</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>participants_attended_moh</t>
+          <t>participants_invited_expert_client</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>participants_attended_asdf</t>
+          <t>participants_invited_adolescent_champion</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>participants_attended_egpaf</t>
+          <t>participants_attended</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>participants_attended_non_pepfar</t>
+          <t>participants_attended_program_mentors</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>facilitators_invited</t>
+          <t>participants_attended_districts_mentors</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>facilitators_invited_moh</t>
+          <t>participants_attended_doctors</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>facilitators_invited_asdf</t>
+          <t>participants_attended_nurses</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>facilitators_invited_egpaf</t>
+          <t>participants_attended_meo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>facilitators_invited_non_pepfar</t>
+          <t>participants_attended_mem</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>facilitators_attended</t>
+          <t>participants_attended_lab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>facilitators_attended_moh</t>
+          <t>participants_attended_stockmgmt</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>facilitators_attended_asdf</t>
+          <t>participants_attended_dataclerk</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>facilitators_attended_egpaf</t>
+          <t>participants_attended_aps</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>facilitators_attended_non_pepfar</t>
+          <t>participants_attended_facilities_staff</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cost_material</t>
+          <t>participants_attended_districts_staff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cost_hall</t>
+          <t>participants_attended_other_org_staff</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cost_food</t>
+          <t>participants_attended_cbo</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cost_lodging</t>
+          <t>participants_attended_chw</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cost_travel</t>
+          <t>participants_attended_mothers_mentors</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cost_transport</t>
+          <t>participants_attended_expert_client</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cost_facilitation</t>
+          <t>participants_attended_adolescent_champion</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
+        <is>
+          <t>participants_invited_moh_central</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>participants_invited_moh_regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>participants_invited_moh_district</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>participants_invited_moh_facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>participants_invited_shac_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>participants_invited_community_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>participants_attended_moh_central</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>participants_attended_moh_regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>participants_attended_moh_district</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>participants_attended_moh_facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>participants_attended_shac_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>participants_attended_community_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>facilitators_invited</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>facilitators_invited_moh_central</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>facilitators_invited_moh_regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>facilitators_invited_moh_district</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>facilitators_invited_moh_facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>facilitators_invited_shac</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>facilitators_invited_community_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>facilitators_invited_other_organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>facilitators_attended</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>facilitators_attended_moh_central</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>facilitators_attended_moh_regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>facilitators_attended_moh_district</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>facilitators_attended_moh_facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>facilitators_attended_shac</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>facilitators_attended_community_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>facilitators_attended_other_organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cost_material</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cost_hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cost_food</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cost_lodging</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cost_travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cost_transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cost_facilitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>files</t>
         </is>
